--- a/output/pdf_financials_xlsx/PATH.xlsx
+++ b/output/pdf_financials_xlsx/PATH.xlsx
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.653783</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.675466</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.675466</v>
       </c>
     </row>
     <row r="93">
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.256991</v>
+        <v>-0.120113</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.105714</v>
+        <v>-0.26584</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1.174072</v>
+        <v>1.010069</v>
       </c>
     </row>
     <row r="119">
@@ -3130,7 +3130,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3887,7 +3891,11 @@
           <t>Reserves (Note 9) 4,675,466</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>4.653783</v>
       </c>
@@ -4495,7 +4503,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -5988,7 +6000,11 @@
           <t>Exploration and evaluation expenditures (371,554)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="n">
         <v>-0.377104</v>
       </c>

--- a/output/pdf_financials_xlsx/PATH.xlsx
+++ b/output/pdf_financials_xlsx/PATH.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.081188</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.142429</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.8682800000000001</v>
+        <v>0.949468</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.36221</v>
+        <v>0.40141</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.01467</v>
+        <v>0.157099</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.097665</v>
+        <v>0.016477</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.042984</v>
+        <v>0.003784</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.150834</v>
+        <v>0.008404999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">

--- a/output/pdf_financials_xlsx/PATH.xlsx
+++ b/output/pdf_financials_xlsx/PATH.xlsx
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.124956</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.016517</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.012973</v>
       </c>
     </row>
     <row r="102">
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.150425</v>
+        <v>0.275381</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.363492</v>
+        <v>0.380009</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.227343</v>
+        <v>0.240316</v>
       </c>
     </row>
     <row r="107">
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.216645</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.28162</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.110452</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.233692</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.260973</v>
       </c>
     </row>
     <row r="116">
@@ -4286,7 +4286,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4346,7 +4350,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -4474,7 +4482,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5740,7 +5752,11 @@
           <t>Accretion expense 281,620</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.216645</v>
       </c>
@@ -5771,7 +5787,11 @@
           <t>GST receivable 16,517</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>0.124956</v>
       </c>
@@ -5938,7 +5958,11 @@
           <t>Proceeds from sale of marketable securities 233,692</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>0.110452</v>
       </c>
